--- a/data/trans_orig/IQ27-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ27-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso medio, en kilogramos, referido por progenitor/a</t>
+          <t>Peso medio, en kilogramos, declarado por progenitor/a (tasa de respuesta: 96,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,3; 32,21</t>
+          <t>27,53; 32,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,85; 32,93</t>
+          <t>26,76; 33,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,95; 30,07</t>
+          <t>23,9; 30,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31,06; 35,86</t>
+          <t>30,96; 35,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,31; 35,38</t>
+          <t>29,16; 35,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,03; 32,89</t>
+          <t>26,49; 33,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,9; 29,21</t>
+          <t>24,37; 29,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,27; 41,39</t>
+          <t>34,2; 41,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,01; 32,99</t>
+          <t>28,9; 32,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,39; 32,05</t>
+          <t>27,54; 32,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,72; 28,99</t>
+          <t>24,98; 29,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,45; 38,1</t>
+          <t>33,49; 37,98</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,66; 29,97</t>
+          <t>24,75; 29,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,82; 29,63</t>
+          <t>24,66; 29,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,39; 31,41</t>
+          <t>26,22; 31,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,91; 37,5</t>
+          <t>31,03; 37,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,34; 32,28</t>
+          <t>26,38; 32,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,88; 32,58</t>
+          <t>26,91; 32,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,62; 31,42</t>
+          <t>26,58; 31,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,16; 40,48</t>
+          <t>34,35; 40,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,21; 30,14</t>
+          <t>26,23; 30,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,5; 30,28</t>
+          <t>26,43; 30,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,96; 30,55</t>
+          <t>27,02; 30,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,39; 37,8</t>
+          <t>33,58; 38,18</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,52; 37,6</t>
+          <t>30,38; 37,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,94; 33,51</t>
+          <t>27,39; 33,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,31; 31,83</t>
+          <t>25,21; 31,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,98; 38,5</t>
+          <t>31,25; 39,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,53; 41,14</t>
+          <t>34,97; 41,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,74; 31,74</t>
+          <t>25,62; 31,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,87; 36,92</t>
+          <t>29,74; 36,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,92; 42,01</t>
+          <t>32,79; 41,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33,94; 38,83</t>
+          <t>33,93; 38,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,22; 31,55</t>
+          <t>27,06; 31,7</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,7; 33,44</t>
+          <t>28,63; 33,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,91; 39,25</t>
+          <t>33,05; 39,3</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,86; 33,76</t>
+          <t>30,09; 34,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,61; 30,54</t>
+          <t>26,64; 30,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,35; 31,91</t>
+          <t>28,6; 32,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,92; 44,61</t>
+          <t>31,93; 45,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,46; 36,09</t>
+          <t>31,5; 36,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,92; 31,86</t>
+          <t>27,92; 31,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,82; 33,06</t>
+          <t>28,94; 33,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,81; 42,12</t>
+          <t>34,78; 42,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,34; 34,34</t>
+          <t>31,28; 34,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,76; 30,47</t>
+          <t>27,79; 30,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,17; 32,01</t>
+          <t>29,2; 31,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,42; 41,9</t>
+          <t>34,51; 41,7</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30,42; 35,73</t>
+          <t>30,6; 35,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,09; 33,66</t>
+          <t>29,16; 33,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,46; 33,71</t>
+          <t>29,34; 33,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31,59; 36,91</t>
+          <t>31,83; 37,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,59; 37,65</t>
+          <t>32,35; 37,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,38; 36,12</t>
+          <t>30,46; 36,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,34; 34,53</t>
+          <t>29,25; 34,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,23; 41,12</t>
+          <t>34,55; 41,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,25; 36,09</t>
+          <t>32,48; 36,15</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,39; 34,2</t>
+          <t>30,42; 34,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,03; 33,57</t>
+          <t>30,13; 33,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,15; 38,55</t>
+          <t>34,27; 38,77</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31,88; 37,92</t>
+          <t>31,64; 37,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,21; 38,28</t>
+          <t>28,74; 38,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,13; 37,25</t>
+          <t>29,19; 37,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31,96; 39,84</t>
+          <t>32,16; 40,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,38; 38,75</t>
+          <t>30,09; 38,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,1; 37,4</t>
+          <t>30,14; 37,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,04; 38,07</t>
+          <t>31,12; 37,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35,08; 44,33</t>
+          <t>35,21; 44,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32,0; 37,09</t>
+          <t>31,92; 37,16</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,91; 36,78</t>
+          <t>30,71; 36,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31,32; 36,63</t>
+          <t>31,07; 36,36</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>34,58; 40,72</t>
+          <t>34,87; 41,29</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30,56; 32,73</t>
+          <t>30,55; 32,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,48; 30,7</t>
+          <t>28,56; 30,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,86; 30,87</t>
+          <t>28,91; 31,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33,28; 38,76</t>
+          <t>33,31; 38,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,6; 35,02</t>
+          <t>32,65; 35,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,4; 31,8</t>
+          <t>29,48; 31,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,64; 31,94</t>
+          <t>29,68; 31,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>36,03; 39,42</t>
+          <t>36,2; 39,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31,98; 33,63</t>
+          <t>31,95; 33,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29,41; 30,98</t>
+          <t>29,41; 30,97</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29,67; 31,23</t>
+          <t>29,61; 31,15</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,24; 38,24</t>
+          <t>35,34; 38,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ27-Clase-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,53; 32,5</t>
+          <t>27,25; 32,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,76; 33,08</t>
+          <t>26,94; 33,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,9; 30,26</t>
+          <t>23,53; 29,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,96; 35,75</t>
+          <t>31,08; 35,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,16; 35,43</t>
+          <t>29,28; 35,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,49; 33,03</t>
+          <t>26,11; 32,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,37; 29,59</t>
+          <t>24,07; 29,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,2; 41,59</t>
+          <t>34,33; 41,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,9; 32,98</t>
+          <t>29,18; 33,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,54; 32,17</t>
+          <t>27,46; 31,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,98; 29,19</t>
+          <t>24,8; 28,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,49; 37,98</t>
+          <t>33,52; 38,03</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,75; 29,92</t>
+          <t>24,58; 29,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,66; 29,85</t>
+          <t>24,65; 29,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,22; 31,21</t>
+          <t>26,16; 31,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,03; 37,22</t>
+          <t>31,32; 37,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,38; 32,42</t>
+          <t>26,36; 32,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,91; 32,35</t>
+          <t>26,65; 32,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,58; 31,4</t>
+          <t>26,7; 31,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,35; 40,57</t>
+          <t>34,5; 40,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,23; 30,17</t>
+          <t>26,3; 30,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,43; 30,32</t>
+          <t>26,39; 30,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,02; 30,49</t>
+          <t>27,16; 30,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,58; 38,18</t>
+          <t>33,64; 37,73</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,38; 37,3</t>
+          <t>30,54; 37,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,39; 33,31</t>
+          <t>27,12; 33,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,21; 31,38</t>
+          <t>25,44; 31,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,25; 39,01</t>
+          <t>30,67; 38,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,97; 41,04</t>
+          <t>34,49; 41,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,62; 31,85</t>
+          <t>25,68; 31,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,74; 36,56</t>
+          <t>29,98; 37,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,79; 41,52</t>
+          <t>33,15; 41,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33,93; 38,96</t>
+          <t>33,8; 38,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,06; 31,7</t>
+          <t>27,26; 31,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,63; 33,44</t>
+          <t>28,64; 33,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33,05; 39,3</t>
+          <t>33,05; 39,53</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,09; 34,09</t>
+          <t>29,89; 33,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,64; 30,57</t>
+          <t>26,55; 30,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,6; 32,13</t>
+          <t>28,61; 32,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,93; 45,26</t>
+          <t>32,09; 45,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,5; 36,01</t>
+          <t>31,43; 36,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,92; 31,7</t>
+          <t>27,87; 31,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,94; 33,16</t>
+          <t>29,04; 33,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,78; 42,19</t>
+          <t>34,87; 42,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,28; 34,32</t>
+          <t>31,22; 34,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,79; 30,57</t>
+          <t>27,63; 30,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,2; 31,82</t>
+          <t>29,17; 31,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,51; 41,7</t>
+          <t>34,28; 42,1</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30,6; 35,9</t>
+          <t>30,34; 35,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,16; 33,92</t>
+          <t>29,11; 33,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,34; 33,96</t>
+          <t>29,59; 33,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31,83; 37,23</t>
+          <t>32,02; 37,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,35; 37,66</t>
+          <t>32,62; 37,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,46; 36,4</t>
+          <t>30,54; 36,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,25; 34,65</t>
+          <t>29,24; 34,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,55; 41,43</t>
+          <t>34,58; 40,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,48; 36,15</t>
+          <t>32,3; 36,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,42; 34,24</t>
+          <t>30,53; 34,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,13; 33,57</t>
+          <t>30,15; 33,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,27; 38,77</t>
+          <t>34,22; 38,68</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31,64; 37,73</t>
+          <t>32,0; 37,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,74; 38,92</t>
+          <t>28,61; 38,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,19; 37,05</t>
+          <t>29,12; 36,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32,16; 40,09</t>
+          <t>31,93; 40,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,09; 38,15</t>
+          <t>30,07; 38,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,14; 37,77</t>
+          <t>30,46; 38,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,12; 37,93</t>
+          <t>31,21; 38,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35,21; 44,33</t>
+          <t>34,98; 44,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31,92; 37,16</t>
+          <t>31,88; 37,08</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,71; 36,76</t>
+          <t>30,65; 36,74</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31,07; 36,36</t>
+          <t>31,39; 36,75</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>34,87; 41,29</t>
+          <t>34,65; 40,87</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30,55; 32,72</t>
+          <t>30,5; 32,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,56; 30,79</t>
+          <t>28,6; 30,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,91; 31,05</t>
+          <t>28,93; 31,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33,31; 38,54</t>
+          <t>33,32; 38,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,65; 35,06</t>
+          <t>32,62; 35,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,48; 31,8</t>
+          <t>29,49; 31,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,68; 31,79</t>
+          <t>29,73; 31,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>36,2; 39,45</t>
+          <t>36,27; 39,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31,95; 33,68</t>
+          <t>31,97; 33,57</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29,41; 30,97</t>
+          <t>29,31; 30,93</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29,61; 31,15</t>
+          <t>29,64; 31,1</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,34; 38,15</t>
+          <t>35,31; 38,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ27-Clase-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32,23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29,5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26,68</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>37,03</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>29,74</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>29,69</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>26,77</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33,38</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>32,23</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29,5</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26,68</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>37,28</t>
+          <t>33,72</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,53</t>
+          <t>35,48</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,25; 32,42</t>
+          <t>29,31; 35,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,94; 33,12</t>
+          <t>26,03; 32,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,53; 29,94</t>
+          <t>23,9; 29,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31,08; 35,88</t>
+          <t>34,29; 40,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,28; 35,34</t>
+          <t>27,3; 32,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,11; 32,9</t>
+          <t>26,85; 32,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,07; 29,5</t>
+          <t>23,95; 30,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,33; 41,03</t>
+          <t>31,44; 36,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,18; 33,24</t>
+          <t>29,01; 32,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,46; 31,95</t>
+          <t>27,39; 32,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,8; 28,84</t>
+          <t>24,72; 28,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,52; 38,03</t>
+          <t>33,36; 37,59</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>29,17</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29,5</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28,93</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>38,09</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>27,13</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>27,16</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>28,69</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>33,99</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>29,17</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>29,5</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>28,93</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37,27</t>
+          <t>34,5</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,64</t>
+          <t>36,25</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,58; 29,9</t>
+          <t>26,34; 32,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,65; 29,69</t>
+          <t>26,88; 32,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,16; 31,18</t>
+          <t>26,62; 31,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,32; 37,33</t>
+          <t>34,98; 41,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,36; 32,23</t>
+          <t>24,66; 29,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,65; 32,36</t>
+          <t>24,82; 29,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,7; 31,46</t>
+          <t>26,39; 31,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,5; 40,73</t>
+          <t>31,4; 38,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,3; 30,27</t>
+          <t>26,21; 30,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,39; 30,23</t>
+          <t>26,5; 30,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,16; 30,43</t>
+          <t>26,96; 30,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,64; 37,73</t>
+          <t>34,01; 38,55</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>37,96</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28,42</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33,26</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>38,66</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>33,76</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>30,06</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>28,39</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>34,59</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>37,96</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,42</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>33,26</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37,18</t>
+          <t>35,21</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,06</t>
+          <t>37,06</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,54; 37,48</t>
+          <t>34,53; 41,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,12; 33,25</t>
+          <t>25,74; 31,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,44; 31,55</t>
+          <t>29,87; 36,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,67; 38,75</t>
+          <t>34,6; 43,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,49; 41,62</t>
+          <t>30,52; 37,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,68; 31,54</t>
+          <t>26,94; 33,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,98; 37,06</t>
+          <t>25,31; 31,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,15; 41,56</t>
+          <t>31,72; 38,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33,8; 38,71</t>
+          <t>33,94; 38,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,26; 31,5</t>
+          <t>27,22; 31,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,64; 33,7</t>
+          <t>28,7; 33,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33,05; 39,53</t>
+          <t>33,94; 40,08</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>33,69</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29,79</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30,89</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>38,62</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>31,85</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>28,39</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>30,23</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>36,26</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>33,69</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,79</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30,89</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,92</t>
+          <t>34,94</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>37,09</t>
+          <t>36,89</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,89; 33,87</t>
+          <t>31,46; 36,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,55; 30,39</t>
+          <t>27,92; 31,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,61; 32,29</t>
+          <t>28,82; 33,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,09; 45,5</t>
+          <t>35,54; 43,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,43; 36,11</t>
+          <t>29,86; 33,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,87; 31,85</t>
+          <t>26,61; 30,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,04; 33,0</t>
+          <t>28,35; 31,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,87; 42,32</t>
+          <t>32,74; 37,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,22; 34,42</t>
+          <t>31,34; 34,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,63; 30,46</t>
+          <t>27,76; 30,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,17; 31,92</t>
+          <t>29,17; 32,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,28; 42,1</t>
+          <t>34,84; 39,27</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>35,08</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33,31</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>31,78</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>38,2</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>33,1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>31,39</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>31,67</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>34,46</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>35,08</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>33,31</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>31,78</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37,46</t>
+          <t>34,82</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36,21</t>
+          <t>36,72</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30,34; 35,86</t>
+          <t>32,59; 37,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,11; 33,85</t>
+          <t>30,38; 36,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,59; 33,88</t>
+          <t>29,34; 34,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32,02; 37,32</t>
+          <t>34,94; 41,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,62; 37,8</t>
+          <t>30,42; 35,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,54; 36,17</t>
+          <t>29,09; 33,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,24; 34,66</t>
+          <t>29,46; 33,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,58; 40,74</t>
+          <t>32,1; 37,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,3; 36,08</t>
+          <t>32,25; 36,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,53; 34,24</t>
+          <t>30,39; 34,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,15; 33,46</t>
+          <t>30,03; 33,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,22; 38,68</t>
+          <t>34,69; 39,01</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>34,14</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>33,98</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34,62</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>41,1</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>34,73</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>33,32</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>33,04</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>35,67</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>34,14</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>33,98</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>34,62</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>39,47</t>
+          <t>37,11</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,64</t>
+          <t>39,11</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,0; 37,97</t>
+          <t>30,38; 38,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,61; 38,75</t>
+          <t>30,1; 37,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,12; 36,98</t>
+          <t>31,04; 38,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31,93; 40,16</t>
+          <t>36,94; 45,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,07; 38,06</t>
+          <t>31,88; 37,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,46; 38,05</t>
+          <t>28,21; 38,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,21; 38,25</t>
+          <t>29,13; 37,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34,98; 44,56</t>
+          <t>33,41; 41,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31,88; 37,08</t>
+          <t>32,0; 37,09</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,65; 36,74</t>
+          <t>30,91; 36,78</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31,39; 36,75</t>
+          <t>31,32; 36,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>34,65; 40,87</t>
+          <t>36,07; 42,14</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>33,85</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>30,64</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>30,75</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>38,45</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>31,59</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>29,64</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>29,96</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>34,97</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>33,85</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>30,64</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>30,75</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>37,72</t>
+          <t>34,91</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>36,43</t>
+          <t>36,78</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30,5; 32,71</t>
+          <t>32,6; 35,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,6; 30,76</t>
+          <t>29,4; 31,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,93; 31,02</t>
+          <t>29,64; 31,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33,32; 38,86</t>
+          <t>36,77; 40,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,62; 35,18</t>
+          <t>30,56; 32,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,49; 31,78</t>
+          <t>28,48; 30,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,73; 31,93</t>
+          <t>28,86; 30,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>36,27; 39,48</t>
+          <t>33,74; 36,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31,97; 33,57</t>
+          <t>31,98; 33,63</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29,31; 30,93</t>
+          <t>29,41; 30,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29,64; 31,1</t>
+          <t>29,67; 31,23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,31; 38,15</t>
+          <t>35,88; 37,81</t>
         </is>
       </c>
     </row>
